--- a/artfynd/A 10619-2023 artfynd.xlsx
+++ b/artfynd/A 10619-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10619-2023 artfynd.xlsx
+++ b/artfynd/A 10619-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104305615</v>
+        <v>107240200</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Konäs, Jmt</t>
+          <t>Konäsån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404450.4798027966</v>
+        <v>404591</v>
       </c>
       <c r="R2" t="n">
-        <v>7052057.091666414</v>
+        <v>7052306</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104396513</v>
+        <v>107240206</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,45 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Konäs, Jmt</t>
+          <t>Konäsån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404410.1670524143</v>
+        <v>404510</v>
       </c>
       <c r="R3" t="n">
-        <v>7052081.474972909</v>
+        <v>7052406</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,73 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104396512</v>
+        <v>107240201</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Konäs, Jmt</t>
+          <t>Konäsån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404448.9810117018</v>
+        <v>404550</v>
       </c>
       <c r="R4" t="n">
-        <v>7052111.050208413</v>
+        <v>7052422</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,27 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104396511</v>
+        <v>107240202</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,45 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Konäs, Jmt</t>
+          <t>Konäsån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404459.8666546694</v>
+        <v>404516</v>
       </c>
       <c r="R5" t="n">
-        <v>7052116.960384977</v>
+        <v>7052400</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,27 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,49 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107240206</v>
+        <v>107240199</v>
       </c>
       <c r="B6" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1215,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>404510.0404779729</v>
+        <v>404600</v>
       </c>
       <c r="R6" t="n">
-        <v>7052405.497242426</v>
+        <v>7052262</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1248,19 +1131,9 @@
           <t>2023-03-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107240199</v>
+        <v>107240205</v>
       </c>
       <c r="B7" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6486</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1327,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404600.7756870117</v>
+        <v>404508</v>
       </c>
       <c r="R7" t="n">
-        <v>7052262.87229334</v>
+        <v>7052399</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1360,19 +1228,9 @@
           <t>2023-03-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,53 +1257,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107240205</v>
+        <v>104305615</v>
       </c>
       <c r="B8" t="n">
-        <v>73691</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Konäsån, Jmt</t>
+          <t>Konäs, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404507.1519244571</v>
+        <v>404451</v>
       </c>
       <c r="R8" t="n">
-        <v>7052398.455826334</v>
+        <v>7052057</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,22 +1330,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,27 +1355,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107240151</v>
+        <v>104396511</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,24 +1396,27 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Konäsån, Jmt</t>
+          <t>Konäs, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404450.4396007094</v>
+        <v>404460</v>
       </c>
       <c r="R9" t="n">
-        <v>7052055.756168589</v>
+        <v>7052117</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,27 +1440,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,27 +1465,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107240202</v>
+        <v>104396512</v>
       </c>
       <c r="B10" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,37 +1488,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Konäsån, Jmt</t>
+          <t>Konäs, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404516.1063336513</v>
+        <v>404449</v>
       </c>
       <c r="R10" t="n">
-        <v>7052399.522973455</v>
+        <v>7052111</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,22 +1550,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,65 +1575,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107240201</v>
+        <v>104396513</v>
       </c>
       <c r="B11" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Konäsån, Jmt</t>
+          <t>Konäs, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404549.7985099602</v>
+        <v>404410</v>
       </c>
       <c r="R11" t="n">
-        <v>7052422.121992063</v>
+        <v>7052081</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,22 +1660,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,27 +1685,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107240204</v>
+        <v>107240151</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,34 +1708,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Konäsån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404514.3234876283</v>
+        <v>404451</v>
       </c>
       <c r="R12" t="n">
-        <v>7052399.576612793</v>
+        <v>7052056</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1930,19 +1770,14 @@
           <t>2023-03-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-03-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,15 +1804,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107240200</v>
+        <v>107240195</v>
       </c>
       <c r="B13" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1985,34 +1815,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Konäsån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404591.3493727507</v>
+        <v>404542</v>
       </c>
       <c r="R13" t="n">
-        <v>7052305.481577516</v>
+        <v>7052235</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2042,19 +1877,14 @@
           <t>2023-03-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-03-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,15 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107312743</v>
+        <v>107240197</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,23 +1940,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Övre konäs S, Jmt</t>
+          <t>Konäsån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404579.4095503356</v>
+        <v>404543</v>
       </c>
       <c r="R14" t="n">
-        <v>7051967.662842032</v>
+        <v>7052236</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2155,27 +1981,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,27 +2006,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107312742</v>
+        <v>107312724</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,11 +2049,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2250,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404614.0240085942</v>
+        <v>404808</v>
       </c>
       <c r="R15" t="n">
-        <v>7051991.129308978</v>
+        <v>7051936</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2283,19 +2090,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2327,15 +2124,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107312733</v>
+        <v>107312725</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2155,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2371,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404568.9869040458</v>
+        <v>404817</v>
       </c>
       <c r="R16" t="n">
-        <v>7051947.479402464</v>
+        <v>7051949</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2404,19 +2200,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2448,15 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107312744</v>
+        <v>107312726</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,10 +2273,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404581.4261488426</v>
+        <v>404828</v>
       </c>
       <c r="R17" t="n">
-        <v>7052049.587981219</v>
+        <v>7051960</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2525,19 +2306,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2569,15 +2340,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107312731</v>
+        <v>107312727</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2373,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2617,10 +2383,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404591.2129577532</v>
+        <v>404817</v>
       </c>
       <c r="R18" t="n">
-        <v>7051929.879063565</v>
+        <v>7052021</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2650,19 +2416,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2694,15 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107312746</v>
+        <v>107312728</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,11 +2481,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2742,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404612.6336833939</v>
+        <v>404778</v>
       </c>
       <c r="R19" t="n">
-        <v>7052033.946186533</v>
+        <v>7051999</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2775,19 +2522,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2819,15 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107312727</v>
+        <v>107312729</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2855,11 +2587,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2867,10 +2595,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>404816.6062824384</v>
+        <v>404747</v>
       </c>
       <c r="R20" t="n">
-        <v>7052021.585110929</v>
+        <v>7051989</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2900,19 +2628,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2944,15 +2662,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107312732</v>
+        <v>107312730</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,10 +2705,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>404556.6122918456</v>
+        <v>404630</v>
       </c>
       <c r="R21" t="n">
-        <v>7051951.416123887</v>
+        <v>7051919</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3025,19 +2738,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3069,15 +2772,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107312739</v>
+        <v>107312731</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3117,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404681.0622223797</v>
+        <v>404591</v>
       </c>
       <c r="R22" t="n">
-        <v>7052084.021887345</v>
+        <v>7051930</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3150,19 +2848,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3194,15 +2882,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107312735</v>
+        <v>107312732</v>
       </c>
       <c r="B23" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +2915,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3242,10 +2925,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404696.918969274</v>
+        <v>404557</v>
       </c>
       <c r="R23" t="n">
-        <v>7052002.897780768</v>
+        <v>7051952</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3275,19 +2958,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3319,15 +2992,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107312745</v>
+        <v>107312733</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3363,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>404586.4633316425</v>
+        <v>404569</v>
       </c>
       <c r="R24" t="n">
-        <v>7052053.892247804</v>
+        <v>7051947</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3396,19 +3064,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3440,15 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>107312741</v>
+        <v>107312734</v>
       </c>
       <c r="B25" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3478,7 +3131,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3488,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404645.1208390708</v>
+        <v>404640</v>
       </c>
       <c r="R25" t="n">
-        <v>7051986.630373158</v>
+        <v>7051966</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3521,24 +3174,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,15 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>107312738</v>
+        <v>107312735</v>
       </c>
       <c r="B26" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3234,11 @@
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3609,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404682.9074796519</v>
+        <v>404697</v>
       </c>
       <c r="R26" t="n">
-        <v>7052100.897834241</v>
+        <v>7052003</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3642,19 +3279,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3686,15 +3313,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>107312747</v>
+        <v>107312736</v>
       </c>
       <c r="B27" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3702,34 +3324,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Övre konäs S, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404745.3142858852</v>
+        <v>404733</v>
       </c>
       <c r="R27" t="n">
-        <v>7052054.468000839</v>
+        <v>7052036</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3759,19 +3385,14 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3798,15 +3419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>107312740</v>
+        <v>107312737</v>
       </c>
       <c r="B28" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3834,11 +3450,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3846,10 +3458,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404685.1501027179</v>
+        <v>404750</v>
       </c>
       <c r="R28" t="n">
-        <v>7052056.719653495</v>
+        <v>7052029</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3879,19 +3491,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3923,15 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>107312729</v>
+        <v>107312738</v>
       </c>
       <c r="B29" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3967,10 +3564,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404747.3623684293</v>
+        <v>404683</v>
       </c>
       <c r="R29" t="n">
-        <v>7051988.90754507</v>
+        <v>7052101</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4000,19 +3597,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4044,15 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>107312734</v>
+        <v>107312739</v>
       </c>
       <c r="B30" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4082,7 +3664,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4092,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404640.4669668833</v>
+        <v>404681</v>
       </c>
       <c r="R30" t="n">
-        <v>7051965.382400781</v>
+        <v>7052084</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4125,19 +3707,14 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4164,15 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>107312728</v>
+        <v>107312740</v>
       </c>
       <c r="B31" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4200,7 +3772,11 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4208,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404778.0085272548</v>
+        <v>404685</v>
       </c>
       <c r="R31" t="n">
-        <v>7051999.127427245</v>
+        <v>7052057</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4241,19 +3817,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4285,15 +3851,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>107312737</v>
+        <v>107312741</v>
       </c>
       <c r="B32" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4321,7 +3882,11 @@
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4329,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404749.9019610134</v>
+        <v>404645</v>
       </c>
       <c r="R32" t="n">
-        <v>7052028.932920325</v>
+        <v>7051986</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4362,19 +3927,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4406,15 +3961,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>107312736</v>
+        <v>107312742</v>
       </c>
       <c r="B33" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4442,7 +3992,11 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4450,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404733.6224948952</v>
+        <v>404614</v>
       </c>
       <c r="R33" t="n">
-        <v>7052036.550596072</v>
+        <v>7051991</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4483,19 +4037,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4527,15 +4071,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>107312730</v>
+        <v>107312743</v>
       </c>
       <c r="B34" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4563,11 +4102,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4575,10 +4110,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404630.1604916348</v>
+        <v>404580</v>
       </c>
       <c r="R34" t="n">
-        <v>7051919.351353147</v>
+        <v>7051967</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4608,19 +4143,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4652,15 +4177,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>107312726</v>
+        <v>107312744</v>
       </c>
       <c r="B35" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4696,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>404828.5830258985</v>
+        <v>404581</v>
       </c>
       <c r="R35" t="n">
-        <v>7051959.736640934</v>
+        <v>7052050</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4729,19 +4249,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4770,6 +4280,333 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>107312745</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Övre konäs S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>404586</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7052054</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>107312746</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Övre konäs S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>404613</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7052034</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4346404</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SV Övre Konäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>404490</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7052350</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2002-07-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2002-07-02</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>taxyta Ö1000</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10619-2023 artfynd.xlsx
+++ b/artfynd/A 10619-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104305615</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396513</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240151</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312724</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312725</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312726</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312727</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312728</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312729</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1753,6 +1803,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312730</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,6 +1918,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312731</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,6 +2033,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312732</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2079,6 +2144,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312733</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2184,6 +2254,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312734</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2294,6 +2369,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312735</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2400,6 +2480,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312736</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2506,6 +2591,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312737</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2612,6 +2702,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312738</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2722,6 +2817,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312739</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2832,6 +2932,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312740</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2942,6 +3047,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312741</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3052,6 +3162,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312742</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3158,6 +3273,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312743</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3264,6 +3384,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312744</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3370,6 +3495,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312745</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3480,6 +3610,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312746</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3577,6 +3712,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240200</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3674,6 +3814,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240206</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3771,6 +3916,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240201</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3868,6 +4018,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240202</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3965,6 +4120,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240199</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4062,6 +4222,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240205</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4172,6 +4337,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396511</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4282,6 +4452,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104396512</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4389,6 +4564,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240195</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4496,6 +4676,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107240197</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4607,8 +4792,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4346404</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>